--- a/data/raw/2026/6月/酒店.xlsx
+++ b/data/raw/2026/6月/酒店.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="26860" windowHeight="11360" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="26860" windowHeight="11760" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问卷数据" sheetId="1" state="visible" r:id="rId1"/>
@@ -1258,7 +1258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA17"/>
+  <dimension ref="A1:CA29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="5.44230769230769" customWidth="1" style="3" min="1" max="1"/>
@@ -1306,7 +1306,7 @@
     <col width="10.4134615384615" customWidth="1" style="3" min="73" max="73"/>
     <col width="14.4615384615385" customWidth="1" style="3" min="74" max="74"/>
     <col width="7.64423076923077" customWidth="1" style="3" min="75" max="75"/>
-    <col width="53.6826923076923" customWidth="1" style="3" min="76" max="76"/>
+    <col width="50.7211538461538" customWidth="1" style="3" min="76" max="76"/>
     <col width="7.71153846153846" customWidth="1" style="3" min="77" max="77"/>
     <col width="23.0480769230769" customWidth="1" style="3" min="78" max="78"/>
   </cols>
@@ -1717,7 +1717,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>284</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1857,12 +1857,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AE2" s="2" t="inlineStr">
@@ -1994,27 +1994,27 @@
       <c r="BM2" s="2" t="inlineStr"/>
       <c r="BN2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22 12:15:24</t>
+          <t>2026-06-30 18:48:26</t>
         </is>
       </c>
       <c r="BO2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22 12:15:24</t>
+          <t>2026-06-30 18:48:26</t>
         </is>
       </c>
       <c r="BP2" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/ca9cf170544e47eeb7d7e898a46017d0.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/7cc304d643b9427e9cfc2e0e16f52e13.mp3</t>
         </is>
       </c>
       <c r="BQ2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 56 秒 </t>
+          <t xml:space="preserve">2 分 53 秒 </t>
         </is>
       </c>
       <c r="BR2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22 12:12:26</t>
+          <t>2026-06-30 18:45:30</t>
         </is>
       </c>
       <c r="BS2" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BW2" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体AT天地(3号门)杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BX2" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>283</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>46-55岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AE3" s="2" t="inlineStr">
@@ -2246,22 +2246,22 @@
       </c>
       <c r="AK3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN3" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO3" s="2" t="inlineStr">
@@ -2343,27 +2343,27 @@
       <c r="BM3" s="2" t="inlineStr"/>
       <c r="BN3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51:53</t>
+          <t>2026-06-30 18:44:50</t>
         </is>
       </c>
       <c r="BO3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51:53</t>
+          <t>2026-06-30 18:44:50</t>
         </is>
       </c>
       <c r="BP3" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/31db1e02827040b5a6127c3c3c7a0048.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/7504544dbb3347cfb4b8c3477c66c626.mp3</t>
         </is>
       </c>
       <c r="BQ3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 56 秒 </t>
+          <t xml:space="preserve">2 分 5 秒 </t>
         </is>
       </c>
       <c r="BR3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11 10:48:54</t>
+          <t>2026-06-30 18:42:42</t>
         </is>
       </c>
       <c r="BS3" s="2" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="BW3" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道滨盛路万象世界中心</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体AT天地(3号门)杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BX3" s="2" t="inlineStr">
@@ -2415,7 +2415,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>282</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -2445,27 +2445,27 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AE4" s="2" t="inlineStr">
@@ -2595,22 +2595,22 @@
       </c>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN4" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO4" s="2" t="inlineStr">
@@ -2692,27 +2692,27 @@
       <c r="BM4" s="2" t="inlineStr"/>
       <c r="BN4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 13:18:18</t>
+          <t>2026-06-30 16:51:19</t>
         </is>
       </c>
       <c r="BO4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 13:18:18</t>
+          <t>2026-06-30 16:51:19</t>
         </is>
       </c>
       <c r="BP4" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/c848f3130ffa4aa7b70c43559a8851a1.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/3289db68c8b540af997196e3c6e2f9c6.mp3</t>
         </is>
       </c>
       <c r="BQ4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 分 16 秒 </t>
+          <t xml:space="preserve">3 分 3 秒 </t>
         </is>
       </c>
       <c r="BR4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 13:14:59</t>
+          <t>2026-06-30 16:48:14</t>
         </is>
       </c>
       <c r="BS4" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>住宿团队</t>
+          <t>散客</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AE5" s="2" t="inlineStr">
@@ -2944,22 +2944,22 @@
       </c>
       <c r="AK5" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO5" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="BG5" s="2" t="inlineStr">
         <is>
-          <t>达到预期</t>
+          <t>超出预期</t>
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr">
@@ -3041,27 +3041,27 @@
       <c r="BM5" s="2" t="inlineStr"/>
       <c r="BN5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 13:01:20</t>
+          <t>2026-06-30 16:42:39</t>
         </is>
       </c>
       <c r="BO5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 13:01:20</t>
+          <t>2026-06-30 16:42:39</t>
         </is>
       </c>
       <c r="BP5" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/1337bdfe227749f48c0a36b44f66aaf5.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/76c847d6bcca4d02bd9fdecc4ac57719.mp3</t>
         </is>
       </c>
       <c r="BQ5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 分 3 秒 </t>
+          <t xml:space="preserve">3 分 1 秒 </t>
         </is>
       </c>
       <c r="BR5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 12:58:14</t>
+          <t>2026-06-30 16:39:35</t>
         </is>
       </c>
       <c r="BS5" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="BW5" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BX5" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>280</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>住宿团队</t>
+          <t>散客</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -3243,22 +3243,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO6" s="2" t="inlineStr">
@@ -3384,33 +3384,37 @@
           <t>会推荐</t>
         </is>
       </c>
-      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr">
+        <is>
+          <t>地下车库找上去的电梯不好找</t>
+        </is>
+      </c>
       <c r="BK6" s="2" t="inlineStr"/>
       <c r="BL6" s="2" t="inlineStr"/>
       <c r="BM6" s="2" t="inlineStr"/>
       <c r="BN6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 12:30:56</t>
+          <t>2026-06-30 16:01:05</t>
         </is>
       </c>
       <c r="BO6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 12:30:56</t>
+          <t>2026-06-30 16:01:05</t>
         </is>
       </c>
       <c r="BP6" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/206b60b4daf54388840bd2a6c7a75e1a.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/d0a0b113a3a8414dba9ae407e93b450a.mp3</t>
         </is>
       </c>
       <c r="BQ6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 分 28 秒 </t>
+          <t xml:space="preserve">2 分 25 秒 </t>
         </is>
       </c>
       <c r="BR6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 12:27:25</t>
+          <t>2026-06-30 15:58:38</t>
         </is>
       </c>
       <c r="BS6" s="2" t="inlineStr">
@@ -3435,7 +3439,7 @@
       </c>
       <c r="BW6" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BX6" s="2" t="inlineStr">
@@ -3462,7 +3466,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>279</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3592,22 +3596,22 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AE7" s="2" t="inlineStr">
@@ -3642,22 +3646,22 @@
       </c>
       <c r="AK7" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL7" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM7" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO7" s="2" t="inlineStr">
@@ -3739,27 +3743,27 @@
       <c r="BM7" s="2" t="inlineStr"/>
       <c r="BN7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 11:44:30</t>
+          <t>2026-06-26 17:19:41</t>
         </is>
       </c>
       <c r="BO7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 11:44:30</t>
+          <t>2026-06-26 17:19:41</t>
         </is>
       </c>
       <c r="BP7" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/af0b874dfb9f4f40acee55aaeffa001c.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/ec58b8eb18b845208e4e48bf3fe2dfa0.mp3</t>
         </is>
       </c>
       <c r="BQ7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 分 24 秒 </t>
+          <t xml:space="preserve">2 分 47 秒 </t>
         </is>
       </c>
       <c r="BR7" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 11:41:03</t>
+          <t>2026-06-26 17:16:50</t>
         </is>
       </c>
       <c r="BS7" s="2" t="inlineStr">
@@ -3784,7 +3788,7 @@
       </c>
       <c r="BW7" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BX7" s="2" t="inlineStr">
@@ -3811,7 +3815,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>278</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3836,7 +3840,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26-35岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3951,12 +3955,12 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AE8" s="2" t="inlineStr">
@@ -3991,22 +3995,22 @@
       </c>
       <c r="AK8" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL8" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM8" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO8" s="2" t="inlineStr">
@@ -4088,27 +4092,27 @@
       <c r="BM8" s="2" t="inlineStr"/>
       <c r="BN8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 11:12:30</t>
+          <t>2026-06-26 16:55:17</t>
         </is>
       </c>
       <c r="BO8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 11:12:30</t>
+          <t>2026-06-26 16:55:17</t>
         </is>
       </c>
       <c r="BP8" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/539f67c7394847f38e4ed7a904bbd915.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/c34e29424ec14a0695a9af2a703a423a.mp3</t>
         </is>
       </c>
       <c r="BQ8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 22 秒 </t>
+          <t xml:space="preserve">4 分 2 秒 </t>
         </is>
       </c>
       <c r="BR8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 11:10:05</t>
+          <t>2026-06-26 16:51:12</t>
         </is>
       </c>
       <c r="BS8" s="2" t="inlineStr">
@@ -4160,7 +4164,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>277</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -4180,12 +4184,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4290,12 +4294,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -4340,22 +4344,22 @@
       </c>
       <c r="AK9" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL9" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM9" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO9" s="2" t="inlineStr">
@@ -4437,27 +4441,27 @@
       <c r="BM9" s="2" t="inlineStr"/>
       <c r="BN9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 11:03:03</t>
+          <t>2026-06-26 13:56:50</t>
         </is>
       </c>
       <c r="BO9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 11:03:03</t>
+          <t>2026-06-26 13:56:50</t>
         </is>
       </c>
       <c r="BP9" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/1635becd5ed443398dea66d96928f274.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/7af6c6a8dbf54e8aa277d5bdfd2b39b9.mp3</t>
         </is>
       </c>
       <c r="BQ9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 9 秒 </t>
+          <t xml:space="preserve">2 分 43 秒 </t>
         </is>
       </c>
       <c r="BR9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 11:00:51</t>
+          <t>2026-06-26 13:54:05</t>
         </is>
       </c>
       <c r="BS9" s="2" t="inlineStr">
@@ -4482,7 +4486,7 @@
       </c>
       <c r="BW9" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道Pet haven哈文宠物生活馆杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BX9" s="2" t="inlineStr">
@@ -4509,7 +4513,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>276</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -4549,12 +4553,12 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -4689,22 +4693,22 @@
       </c>
       <c r="AK10" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL10" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM10" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO10" s="2" t="inlineStr">
@@ -4786,27 +4790,27 @@
       <c r="BM10" s="2" t="inlineStr"/>
       <c r="BN10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 10:55:08</t>
+          <t>2026-06-26 13:40:21</t>
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 10:55:08</t>
+          <t>2026-06-26 13:40:21</t>
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/a4dd0b1c286a42f9ada06a7fc39b2920.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/118be2c5d2994d53abbb256afa496b27.mp3</t>
         </is>
       </c>
       <c r="BQ10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 58 秒 </t>
+          <t xml:space="preserve">2 分 1 秒 </t>
         </is>
       </c>
       <c r="BR10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 10:53:07</t>
+          <t>2026-06-26 13:38:17</t>
         </is>
       </c>
       <c r="BS10" s="2" t="inlineStr">
@@ -4858,7 +4862,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>275</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -4878,12 +4882,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46-55岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4908,7 +4912,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4988,12 +4992,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -5038,22 +5042,22 @@
       </c>
       <c r="AK11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO11" s="2" t="inlineStr">
@@ -5135,27 +5139,27 @@
       <c r="BM11" s="2" t="inlineStr"/>
       <c r="BN11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 18:30:21</t>
+          <t>2026-06-26 13:07:47</t>
         </is>
       </c>
       <c r="BO11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 18:30:21</t>
+          <t>2026-06-26 13:07:47</t>
         </is>
       </c>
       <c r="BP11" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/fc77f000748948e2b27937bcfb5dd8fa.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/34e3979b05bc416fb9056bd3ea48f8d2.mp3</t>
         </is>
       </c>
       <c r="BQ11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 2 秒 </t>
+          <t xml:space="preserve">2 分 1 秒 </t>
         </is>
       </c>
       <c r="BR11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 18:28:17</t>
+          <t>2026-06-26 13:05:43</t>
         </is>
       </c>
       <c r="BS11" s="2" t="inlineStr">
@@ -5180,7 +5184,7 @@
       </c>
       <c r="BW11" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道XDS喜德盛自行车(杭州形象店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BX11" s="2" t="inlineStr">
@@ -5207,7 +5211,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -5227,7 +5231,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -5337,22 +5341,22 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" s="2" t="inlineStr">
@@ -5387,22 +5391,22 @@
       </c>
       <c r="AK12" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL12" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM12" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO12" s="2" t="inlineStr">
@@ -5484,27 +5488,27 @@
       <c r="BM12" s="2" t="inlineStr"/>
       <c r="BN12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 18:15:58</t>
+          <t>2026-06-26 12:32:12</t>
         </is>
       </c>
       <c r="BO12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 18:15:58</t>
+          <t>2026-06-26 12:32:12</t>
         </is>
       </c>
       <c r="BP12" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/0a2c7b14a34d43d49040a6e7b4ebe517.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/2024e1ac542c4e9f93d7e4a68c21b378.mp3</t>
         </is>
       </c>
       <c r="BQ12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 分 31 秒 </t>
+          <t xml:space="preserve">2 分 20 秒 </t>
         </is>
       </c>
       <c r="BR12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 18:12:24</t>
+          <t>2026-06-26 12:29:50</t>
         </is>
       </c>
       <c r="BS12" s="2" t="inlineStr">
@@ -5529,7 +5533,7 @@
       </c>
       <c r="BW12" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭博外环西路杭州奥体博览城</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BX12" s="2" t="inlineStr">
@@ -5556,7 +5560,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>273</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -5696,12 +5700,12 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE13" s="2" t="inlineStr">
@@ -5736,22 +5740,22 @@
       </c>
       <c r="AK13" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL13" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM13" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO13" s="2" t="inlineStr">
@@ -5833,27 +5837,27 @@
       <c r="BM13" s="2" t="inlineStr"/>
       <c r="BN13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 17:38:29</t>
+          <t>2026-06-26 12:12:27</t>
         </is>
       </c>
       <c r="BO13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 17:38:29</t>
+          <t>2026-06-26 12:12:27</t>
         </is>
       </c>
       <c r="BP13" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/c4a779b692b54623bdc699a31d4f5844.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/9464e89bd4a84c9589fab337e4b92669.mp3</t>
         </is>
       </c>
       <c r="BQ13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 </t>
+          <t xml:space="preserve">2 分 41 秒 </t>
         </is>
       </c>
       <c r="BR13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 17:36:27</t>
+          <t>2026-06-26 12:09:43</t>
         </is>
       </c>
       <c r="BS13" s="2" t="inlineStr">
@@ -5878,7 +5882,7 @@
       </c>
       <c r="BW13" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道Pet haven哈文宠物生活馆杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BX13" s="2" t="inlineStr">
@@ -5905,7 +5909,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>272</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -5915,7 +5919,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>住宿团队</t>
+          <t>散客</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -5955,7 +5959,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -6035,22 +6039,22 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE14" s="2" t="inlineStr">
@@ -6085,22 +6089,22 @@
       </c>
       <c r="AK14" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL14" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM14" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN14" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO14" s="2" t="inlineStr">
@@ -6153,12 +6157,12 @@
       <c r="BD14" s="2" t="inlineStr"/>
       <c r="BE14" s="2" t="inlineStr">
         <is>
-          <t>比较满意</t>
+          <t>非常满意</t>
         </is>
       </c>
       <c r="BF14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BG14" s="2" t="inlineStr">
@@ -6182,27 +6186,27 @@
       <c r="BM14" s="2" t="inlineStr"/>
       <c r="BN14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 16:39:13</t>
+          <t>2026-06-22 12:15:24</t>
         </is>
       </c>
       <c r="BO14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 16:39:13</t>
+          <t>2026-06-22 12:15:24</t>
         </is>
       </c>
       <c r="BP14" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/08bfbac963fd4beaa64637cc8e470e51.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/ca9cf170544e47eeb7d7e898a46017d0.mp3</t>
         </is>
       </c>
       <c r="BQ14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 34 秒 </t>
+          <t xml:space="preserve">2 分 56 秒 </t>
         </is>
       </c>
       <c r="BR14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 16:36:36</t>
+          <t>2026-06-22 12:12:26</t>
         </is>
       </c>
       <c r="BS14" s="2" t="inlineStr">
@@ -6227,7 +6231,7 @@
       </c>
       <c r="BW14" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BX14" s="2" t="inlineStr">
@@ -6254,7 +6258,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>271</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -6274,12 +6278,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>46-55岁</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6394,12 +6398,12 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE15" s="2" t="inlineStr">
@@ -6531,27 +6535,27 @@
       <c r="BM15" s="2" t="inlineStr"/>
       <c r="BN15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 16:29:35</t>
+          <t>2026-06-11 10:51:53</t>
         </is>
       </c>
       <c r="BO15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 16:29:35</t>
+          <t>2026-06-11 10:51:53</t>
         </is>
       </c>
       <c r="BP15" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/35d3b3b5f493491192d33585c8d38787.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/31db1e02827040b5a6127c3c3c7a0048.mp3</t>
         </is>
       </c>
       <c r="BQ15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 分 3 秒 </t>
+          <t xml:space="preserve">2 分 56 秒 </t>
         </is>
       </c>
       <c r="BR15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 16:26:29</t>
+          <t>2026-06-11 10:48:54</t>
         </is>
       </c>
       <c r="BS15" s="2" t="inlineStr">
@@ -6576,7 +6580,7 @@
       </c>
       <c r="BW15" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路万象世界中心</t>
         </is>
       </c>
       <c r="BX15" s="2" t="inlineStr">
@@ -6603,7 +6607,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>270</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -6733,22 +6737,22 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE16" s="2" t="inlineStr">
@@ -6880,27 +6884,27 @@
       <c r="BM16" s="2" t="inlineStr"/>
       <c r="BN16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:02</t>
+          <t>2026-06-09 13:18:18</t>
         </is>
       </c>
       <c r="BO16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:02</t>
+          <t>2026-06-09 13:18:18</t>
         </is>
       </c>
       <c r="BP16" s="2" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/19f962c14c834f8fbdfcecafc28f5bcc.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/c848f3130ffa4aa7b70c43559a8851a1.mp3</t>
         </is>
       </c>
       <c r="BQ16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 31 秒 </t>
+          <t xml:space="preserve">3 分 16 秒 </t>
         </is>
       </c>
       <c r="BR16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08 14:59:29</t>
+          <t>2026-06-09 13:14:59</t>
         </is>
       </c>
       <c r="BS16" s="2" t="inlineStr">
@@ -6925,7 +6929,7 @@
       </c>
       <c r="BW16" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道滨盛路万象世界中心</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BX16" s="2" t="inlineStr">
@@ -6952,7 +6956,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>269</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -6972,7 +6976,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7082,22 +7086,22 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE17" s="2" t="inlineStr">
@@ -7152,12 +7156,12 @@
       </c>
       <c r="AO17" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AP17" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AQ17" s="2" t="inlineStr">
@@ -7229,70 +7233,4258 @@
       <c r="BM17" s="2" t="inlineStr"/>
       <c r="BN17" s="2" t="inlineStr">
         <is>
+          <t>2026-06-09 13:01:20</t>
+        </is>
+      </c>
+      <c r="BO17" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09 13:01:20</t>
+        </is>
+      </c>
+      <c r="BP17" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/1337bdfe227749f48c0a36b44f66aaf5.mp3</t>
+        </is>
+      </c>
+      <c r="BQ17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 分 3 秒 </t>
+        </is>
+      </c>
+      <c r="BR17" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:58:14</t>
+        </is>
+      </c>
+      <c r="BS17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU17" s="2" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="BV17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW17" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BX17" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BY17" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BZ17" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="CA17" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM18" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AN18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO18" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP18" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ18" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR18" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS18" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT18" s="2" t="inlineStr"/>
+      <c r="AU18" s="2" t="inlineStr"/>
+      <c r="AV18" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AW18" s="2" t="inlineStr"/>
+      <c r="AX18" s="2" t="inlineStr"/>
+      <c r="AY18" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AZ18" s="2" t="inlineStr"/>
+      <c r="BA18" s="2" t="inlineStr"/>
+      <c r="BB18" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BC18" s="2" t="inlineStr"/>
+      <c r="BD18" s="2" t="inlineStr"/>
+      <c r="BE18" s="2" t="inlineStr">
+        <is>
+          <t>比较满意</t>
+        </is>
+      </c>
+      <c r="BF18" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BG18" s="2" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH18" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI18" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BJ18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr"/>
+      <c r="BL18" s="2" t="inlineStr"/>
+      <c r="BM18" s="2" t="inlineStr"/>
+      <c r="BN18" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:30:56</t>
+        </is>
+      </c>
+      <c r="BO18" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:30:56</t>
+        </is>
+      </c>
+      <c r="BP18" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/206b60b4daf54388840bd2a6c7a75e1a.mp3</t>
+        </is>
+      </c>
+      <c r="BQ18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 分 28 秒 </t>
+        </is>
+      </c>
+      <c r="BR18" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:27:25</t>
+        </is>
+      </c>
+      <c r="BS18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU18" s="2" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="BV18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW18" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BX18" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BY18" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BZ18" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="CA18" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO19" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP19" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ19" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR19" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS19" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT19" s="2" t="inlineStr"/>
+      <c r="AU19" s="2" t="inlineStr"/>
+      <c r="AV19" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AW19" s="2" t="inlineStr"/>
+      <c r="AX19" s="2" t="inlineStr"/>
+      <c r="AY19" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AZ19" s="2" t="inlineStr"/>
+      <c r="BA19" s="2" t="inlineStr"/>
+      <c r="BB19" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BC19" s="2" t="inlineStr"/>
+      <c r="BD19" s="2" t="inlineStr"/>
+      <c r="BE19" s="2" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG19" s="2" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI19" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BJ19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr"/>
+      <c r="BL19" s="2" t="inlineStr"/>
+      <c r="BM19" s="2" t="inlineStr"/>
+      <c r="BN19" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:44:30</t>
+        </is>
+      </c>
+      <c r="BO19" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:44:30</t>
+        </is>
+      </c>
+      <c r="BP19" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/af0b874dfb9f4f40acee55aaeffa001c.mp3</t>
+        </is>
+      </c>
+      <c r="BQ19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 分 24 秒 </t>
+        </is>
+      </c>
+      <c r="BR19" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:41:03</t>
+        </is>
+      </c>
+      <c r="BS19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU19" s="2" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="BV19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW19" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BX19" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BY19" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BZ19" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="CA19" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>26-35岁</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO20" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP20" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ20" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR20" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS20" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT20" s="2" t="inlineStr"/>
+      <c r="AU20" s="2" t="inlineStr"/>
+      <c r="AV20" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AW20" s="2" t="inlineStr"/>
+      <c r="AX20" s="2" t="inlineStr"/>
+      <c r="AY20" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AZ20" s="2" t="inlineStr"/>
+      <c r="BA20" s="2" t="inlineStr"/>
+      <c r="BB20" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BC20" s="2" t="inlineStr"/>
+      <c r="BD20" s="2" t="inlineStr"/>
+      <c r="BE20" s="2" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG20" s="2" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH20" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI20" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BJ20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr"/>
+      <c r="BL20" s="2" t="inlineStr"/>
+      <c r="BM20" s="2" t="inlineStr"/>
+      <c r="BN20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:12:30</t>
+        </is>
+      </c>
+      <c r="BO20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:12:30</t>
+        </is>
+      </c>
+      <c r="BP20" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/539f67c7394847f38e4ed7a904bbd915.mp3</t>
+        </is>
+      </c>
+      <c r="BQ20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 22 秒 </t>
+        </is>
+      </c>
+      <c r="BR20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:10:05</t>
+        </is>
+      </c>
+      <c r="BS20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU20" s="2" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="BV20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW20" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BX20" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BY20" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BZ20" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="CA20" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO21" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP21" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ21" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR21" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS21" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT21" s="2" t="inlineStr"/>
+      <c r="AU21" s="2" t="inlineStr"/>
+      <c r="AV21" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AW21" s="2" t="inlineStr"/>
+      <c r="AX21" s="2" t="inlineStr"/>
+      <c r="AY21" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AZ21" s="2" t="inlineStr"/>
+      <c r="BA21" s="2" t="inlineStr"/>
+      <c r="BB21" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BC21" s="2" t="inlineStr"/>
+      <c r="BD21" s="2" t="inlineStr"/>
+      <c r="BE21" s="2" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG21" s="2" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI21" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BJ21" s="2" t="inlineStr"/>
+      <c r="BK21" s="2" t="inlineStr"/>
+      <c r="BL21" s="2" t="inlineStr"/>
+      <c r="BM21" s="2" t="inlineStr"/>
+      <c r="BN21" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:03:03</t>
+        </is>
+      </c>
+      <c r="BO21" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:03:03</t>
+        </is>
+      </c>
+      <c r="BP21" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/1635becd5ed443398dea66d96928f274.mp3</t>
+        </is>
+      </c>
+      <c r="BQ21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 9 秒 </t>
+        </is>
+      </c>
+      <c r="BR21" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:00:51</t>
+        </is>
+      </c>
+      <c r="BS21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU21" s="2" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="BV21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW21" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BX21" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BY21" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BZ21" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="CA21" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO22" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP22" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ22" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR22" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS22" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT22" s="2" t="inlineStr"/>
+      <c r="AU22" s="2" t="inlineStr"/>
+      <c r="AV22" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AW22" s="2" t="inlineStr"/>
+      <c r="AX22" s="2" t="inlineStr"/>
+      <c r="AY22" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AZ22" s="2" t="inlineStr"/>
+      <c r="BA22" s="2" t="inlineStr"/>
+      <c r="BB22" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BC22" s="2" t="inlineStr"/>
+      <c r="BD22" s="2" t="inlineStr"/>
+      <c r="BE22" s="2" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG22" s="2" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH22" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI22" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BJ22" s="2" t="inlineStr"/>
+      <c r="BK22" s="2" t="inlineStr"/>
+      <c r="BL22" s="2" t="inlineStr"/>
+      <c r="BM22" s="2" t="inlineStr"/>
+      <c r="BN22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09 10:55:08</t>
+        </is>
+      </c>
+      <c r="BO22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09 10:55:08</t>
+        </is>
+      </c>
+      <c r="BP22" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/a4dd0b1c286a42f9ada06a7fc39b2920.mp3</t>
+        </is>
+      </c>
+      <c r="BQ22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 分 58 秒 </t>
+        </is>
+      </c>
+      <c r="BR22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09 10:53:07</t>
+        </is>
+      </c>
+      <c r="BS22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU22" s="2" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="BV22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW22" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BX22" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BY22" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BZ22" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="CA22" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>46-55岁</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AE23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO23" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP23" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ23" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR23" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS23" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT23" s="2" t="inlineStr"/>
+      <c r="AU23" s="2" t="inlineStr"/>
+      <c r="AV23" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AW23" s="2" t="inlineStr"/>
+      <c r="AX23" s="2" t="inlineStr"/>
+      <c r="AY23" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AZ23" s="2" t="inlineStr"/>
+      <c r="BA23" s="2" t="inlineStr"/>
+      <c r="BB23" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BC23" s="2" t="inlineStr"/>
+      <c r="BD23" s="2" t="inlineStr"/>
+      <c r="BE23" s="2" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF23" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG23" s="2" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH23" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI23" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BJ23" s="2" t="inlineStr"/>
+      <c r="BK23" s="2" t="inlineStr"/>
+      <c r="BL23" s="2" t="inlineStr"/>
+      <c r="BM23" s="2" t="inlineStr"/>
+      <c r="BN23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 18:30:21</t>
+        </is>
+      </c>
+      <c r="BO23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 18:30:21</t>
+        </is>
+      </c>
+      <c r="BP23" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/fc77f000748948e2b27937bcfb5dd8fa.mp3</t>
+        </is>
+      </c>
+      <c r="BQ23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 2 秒 </t>
+        </is>
+      </c>
+      <c r="BR23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 18:28:17</t>
+        </is>
+      </c>
+      <c r="BS23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU23" s="2" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="BV23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW23" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道XDS喜德盛自行车(杭州形象店)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BX23" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BY23" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BZ23" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="CA23" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AE24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO24" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP24" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ24" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR24" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS24" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT24" s="2" t="inlineStr"/>
+      <c r="AU24" s="2" t="inlineStr"/>
+      <c r="AV24" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AW24" s="2" t="inlineStr"/>
+      <c r="AX24" s="2" t="inlineStr"/>
+      <c r="AY24" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AZ24" s="2" t="inlineStr"/>
+      <c r="BA24" s="2" t="inlineStr"/>
+      <c r="BB24" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BC24" s="2" t="inlineStr"/>
+      <c r="BD24" s="2" t="inlineStr"/>
+      <c r="BE24" s="2" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF24" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG24" s="2" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI24" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BJ24" s="2" t="inlineStr"/>
+      <c r="BK24" s="2" t="inlineStr"/>
+      <c r="BL24" s="2" t="inlineStr"/>
+      <c r="BM24" s="2" t="inlineStr"/>
+      <c r="BN24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 18:15:58</t>
+        </is>
+      </c>
+      <c r="BO24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 18:15:58</t>
+        </is>
+      </c>
+      <c r="BP24" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/0a2c7b14a34d43d49040a6e7b4ebe517.mp3</t>
+        </is>
+      </c>
+      <c r="BQ24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 分 31 秒 </t>
+        </is>
+      </c>
+      <c r="BR24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 18:12:24</t>
+        </is>
+      </c>
+      <c r="BS24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU24" s="2" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="BV24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW24" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道杭博外环西路杭州奥体博览城</t>
+        </is>
+      </c>
+      <c r="BX24" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BY24" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BZ24" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="CA24" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AE25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO25" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP25" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ25" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR25" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS25" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT25" s="2" t="inlineStr"/>
+      <c r="AU25" s="2" t="inlineStr"/>
+      <c r="AV25" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AW25" s="2" t="inlineStr"/>
+      <c r="AX25" s="2" t="inlineStr"/>
+      <c r="AY25" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AZ25" s="2" t="inlineStr"/>
+      <c r="BA25" s="2" t="inlineStr"/>
+      <c r="BB25" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BC25" s="2" t="inlineStr"/>
+      <c r="BD25" s="2" t="inlineStr"/>
+      <c r="BE25" s="2" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG25" s="2" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI25" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BJ25" s="2" t="inlineStr"/>
+      <c r="BK25" s="2" t="inlineStr"/>
+      <c r="BL25" s="2" t="inlineStr"/>
+      <c r="BM25" s="2" t="inlineStr"/>
+      <c r="BN25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 17:38:29</t>
+        </is>
+      </c>
+      <c r="BO25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 17:38:29</t>
+        </is>
+      </c>
+      <c r="BP25" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/c4a779b692b54623bdc699a31d4f5844.mp3</t>
+        </is>
+      </c>
+      <c r="BQ25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 </t>
+        </is>
+      </c>
+      <c r="BR25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 17:36:27</t>
+        </is>
+      </c>
+      <c r="BS25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU25" s="2" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="BV25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW25" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BX25" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BY25" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BZ25" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="CA25" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AE26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN26" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO26" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP26" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ26" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR26" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS26" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT26" s="2" t="inlineStr"/>
+      <c r="AU26" s="2" t="inlineStr"/>
+      <c r="AV26" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AW26" s="2" t="inlineStr"/>
+      <c r="AX26" s="2" t="inlineStr"/>
+      <c r="AY26" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AZ26" s="2" t="inlineStr"/>
+      <c r="BA26" s="2" t="inlineStr"/>
+      <c r="BB26" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BC26" s="2" t="inlineStr"/>
+      <c r="BD26" s="2" t="inlineStr"/>
+      <c r="BE26" s="2" t="inlineStr">
+        <is>
+          <t>比较满意</t>
+        </is>
+      </c>
+      <c r="BF26" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BG26" s="2" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI26" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BJ26" s="2" t="inlineStr"/>
+      <c r="BK26" s="2" t="inlineStr"/>
+      <c r="BL26" s="2" t="inlineStr"/>
+      <c r="BM26" s="2" t="inlineStr"/>
+      <c r="BN26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 16:39:13</t>
+        </is>
+      </c>
+      <c r="BO26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 16:39:13</t>
+        </is>
+      </c>
+      <c r="BP26" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/08bfbac963fd4beaa64637cc8e470e51.mp3</t>
+        </is>
+      </c>
+      <c r="BQ26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 34 秒 </t>
+        </is>
+      </c>
+      <c r="BR26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 16:36:36</t>
+        </is>
+      </c>
+      <c r="BS26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU26" s="2" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="BV26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW26" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BX26" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BY26" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BZ26" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="CA26" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AE27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO27" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP27" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ27" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR27" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS27" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT27" s="2" t="inlineStr"/>
+      <c r="AU27" s="2" t="inlineStr"/>
+      <c r="AV27" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AW27" s="2" t="inlineStr"/>
+      <c r="AX27" s="2" t="inlineStr"/>
+      <c r="AY27" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AZ27" s="2" t="inlineStr"/>
+      <c r="BA27" s="2" t="inlineStr"/>
+      <c r="BB27" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BC27" s="2" t="inlineStr"/>
+      <c r="BD27" s="2" t="inlineStr"/>
+      <c r="BE27" s="2" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF27" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG27" s="2" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI27" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BJ27" s="2" t="inlineStr"/>
+      <c r="BK27" s="2" t="inlineStr"/>
+      <c r="BL27" s="2" t="inlineStr"/>
+      <c r="BM27" s="2" t="inlineStr"/>
+      <c r="BN27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 16:29:35</t>
+        </is>
+      </c>
+      <c r="BO27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 16:29:35</t>
+        </is>
+      </c>
+      <c r="BP27" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/35d3b3b5f493491192d33585c8d38787.mp3</t>
+        </is>
+      </c>
+      <c r="BQ27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 分 3 秒 </t>
+        </is>
+      </c>
+      <c r="BR27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 16:26:29</t>
+        </is>
+      </c>
+      <c r="BS27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU27" s="2" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="BV27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW27" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BX27" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BY27" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BZ27" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="CA27" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO28" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP28" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ28" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR28" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS28" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT28" s="2" t="inlineStr"/>
+      <c r="AU28" s="2" t="inlineStr"/>
+      <c r="AV28" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AW28" s="2" t="inlineStr"/>
+      <c r="AX28" s="2" t="inlineStr"/>
+      <c r="AY28" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AZ28" s="2" t="inlineStr"/>
+      <c r="BA28" s="2" t="inlineStr"/>
+      <c r="BB28" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BC28" s="2" t="inlineStr"/>
+      <c r="BD28" s="2" t="inlineStr"/>
+      <c r="BE28" s="2" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG28" s="2" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI28" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BJ28" s="2" t="inlineStr"/>
+      <c r="BK28" s="2" t="inlineStr"/>
+      <c r="BL28" s="2" t="inlineStr"/>
+      <c r="BM28" s="2" t="inlineStr"/>
+      <c r="BN28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 15:02:02</t>
+        </is>
+      </c>
+      <c r="BO28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 15:02:02</t>
+        </is>
+      </c>
+      <c r="BP28" s="2" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/19f962c14c834f8fbdfcecafc28f5bcc.mp3</t>
+        </is>
+      </c>
+      <c r="BQ28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 31 秒 </t>
+        </is>
+      </c>
+      <c r="BR28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 14:59:29</t>
+        </is>
+      </c>
+      <c r="BS28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU28" s="2" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="BV28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW28" s="2" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路万象世界中心</t>
+        </is>
+      </c>
+      <c r="BX28" s="2" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BY28" s="2" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+      <c r="BZ28" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="CA28" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AP29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AQ29" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR29" s="2" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS29" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT29" s="2" t="inlineStr"/>
+      <c r="AU29" s="2" t="inlineStr"/>
+      <c r="AV29" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AW29" s="2" t="inlineStr"/>
+      <c r="AX29" s="2" t="inlineStr"/>
+      <c r="AY29" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AZ29" s="2" t="inlineStr"/>
+      <c r="BA29" s="2" t="inlineStr"/>
+      <c r="BB29" s="2" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BC29" s="2" t="inlineStr"/>
+      <c r="BD29" s="2" t="inlineStr"/>
+      <c r="BE29" s="2" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF29" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG29" s="2" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI29" s="2" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BJ29" s="2" t="inlineStr"/>
+      <c r="BK29" s="2" t="inlineStr"/>
+      <c r="BL29" s="2" t="inlineStr"/>
+      <c r="BM29" s="2" t="inlineStr"/>
+      <c r="BN29" s="2" t="inlineStr">
+        <is>
           <t>2026-06-08 14:51:31</t>
         </is>
       </c>
-      <c r="BO17" s="2" t="inlineStr">
+      <c r="BO29" s="2" t="inlineStr">
         <is>
           <t>2026-06-08 14:51:31</t>
         </is>
       </c>
-      <c r="BP17" s="2" t="inlineStr">
+      <c r="BP29" s="2" t="inlineStr">
         <is>
           <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/82aa50da7568420d86d339c23d6a94a9.mp3</t>
         </is>
       </c>
-      <c r="BQ17" s="2" t="inlineStr">
+      <c r="BQ29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2 分 35 秒 </t>
         </is>
       </c>
-      <c r="BR17" s="2" t="inlineStr">
+      <c r="BR29" s="2" t="inlineStr">
         <is>
           <t>2026-06-08 14:48:52</t>
         </is>
       </c>
-      <c r="BS17" s="2" t="inlineStr">
+      <c r="BS29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BT17" s="2" t="inlineStr">
+      <c r="BT29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BU17" s="2" t="inlineStr">
+      <c r="BU29" s="2" t="inlineStr">
         <is>
           <t>0,286,289,302</t>
         </is>
       </c>
-      <c r="BV17" s="2" t="inlineStr">
+      <c r="BV29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BW17" s="2" t="inlineStr">
+      <c r="BW29" s="2" t="inlineStr">
         <is>
           <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
-      <c r="BX17" s="2" t="inlineStr">
+      <c r="BX29" s="2" t="inlineStr">
         <is>
           <t>杭博访问员2</t>
         </is>
       </c>
-      <c r="BY17" s="2" t="inlineStr">
+      <c r="BY29" s="2" t="inlineStr">
         <is>
           <t>一期</t>
         </is>
       </c>
-      <c r="BZ17" s="4" t="inlineStr">
+      <c r="BZ29" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="CA17" s="4" t="inlineStr">
+      <c r="CA29" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
